--- a/data/obx_xlsx/AFGA.OL.xlsx
+++ b/data/obx_xlsx/AFGA.OL.xlsx
@@ -12891,8 +12891,14 @@
       <c r="Q68" s="15">
         <v>308.0</v>
       </c>
-      <c r="R68" s="14"/>
-      <c r="S68" s="14"/>
+      <c r="R68" s="14">
+        <f t="shared" ref="R68:S68" si="1">R69+R73</f>
+        <v>748.36</v>
+      </c>
+      <c r="S68" s="14">
+        <f t="shared" si="1"/>
+        <v>463</v>
+      </c>
       <c r="T68" s="15">
         <v>302.56</v>
       </c>
@@ -17612,8 +17618,12 @@
       <c r="T164" s="15">
         <v>159.09</v>
       </c>
-      <c r="U164" s="14"/>
-      <c r="V164" s="14"/>
+      <c r="U164" s="15">
+        <v>214.1</v>
+      </c>
+      <c r="V164" s="16">
+        <v>95.28</v>
+      </c>
       <c r="W164" s="15">
         <v>132.71</v>
       </c>
